--- a/data/trans_dic/P36B02_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36B02_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>88,25%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>91,42; 96,06</t>
+          <t>91,71; 96,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>92,52; 96,52</t>
+          <t>92,31; 96,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92,38; 96,81</t>
+          <t>92,0; 96,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81,78; 92,32</t>
+          <t>79,76; 91,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,96; 95,37</t>
+          <t>90,92; 95,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,64; 94,67</t>
+          <t>89,55; 94,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,61; 93,9</t>
+          <t>88,73; 93,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>86,54; 94,76</t>
+          <t>85,59; 94,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91,94; 94,98</t>
+          <t>92,18; 95,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91,64; 95,03</t>
+          <t>91,85; 95,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91,32; 94,79</t>
+          <t>91,4; 94,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,35; 92,77</t>
+          <t>84,29; 91,19</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>88,08%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>92,37; 95,86</t>
+          <t>92,21; 95,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90,75; 94,81</t>
+          <t>90,4; 94,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86,46; 91,69</t>
+          <t>86,5; 91,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81,52; 89,89</t>
+          <t>82,89; 90,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>92,3; 96,05</t>
+          <t>92,21; 96,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,29; 93,88</t>
+          <t>89,17; 93,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,75; 95,53</t>
+          <t>91,63; 95,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>45,39; 89,8</t>
+          <t>85,9; 91,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>92,84; 95,49</t>
+          <t>93,05; 95,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90,78; 93,73</t>
+          <t>90,82; 93,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89,93; 93,13</t>
+          <t>89,91; 93,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>61,12; 88,35</t>
+          <t>85,35; 90,32</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89,35; 93,84</t>
+          <t>89,1; 93,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,34; 95,43</t>
+          <t>91,18; 95,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87,99; 92,76</t>
+          <t>87,91; 92,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83,98; 90,43</t>
+          <t>84,46; 90,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>92,49; 95,96</t>
+          <t>92,45; 96,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91,91; 95,61</t>
+          <t>91,96; 95,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92,23; 95,8</t>
+          <t>92,24; 95,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85,29; 89,86</t>
+          <t>84,81; 89,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91,46; 94,33</t>
+          <t>91,53; 94,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92,26; 95,02</t>
+          <t>92,37; 95,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>90,92; 93,89</t>
+          <t>90,67; 93,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>85,54; 89,54</t>
+          <t>85,74; 89,37</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>88,22%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>88,46; 93,85</t>
+          <t>88,29; 93,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>89,89; 94,49</t>
+          <t>89,67; 94,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,07; 92,01</t>
+          <t>86,92; 91,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86,08; 95,71</t>
+          <t>84,48; 89,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,91; 95,94</t>
+          <t>92,0; 96,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,42; 95,64</t>
+          <t>91,34; 95,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,65; 94,68</t>
+          <t>90,43; 94,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>87,6; 91,57</t>
+          <t>87,28; 90,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91,16; 94,39</t>
+          <t>91,04; 94,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91,35; 94,49</t>
+          <t>91,41; 94,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89,48; 92,75</t>
+          <t>89,59; 92,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,83; 93,71</t>
+          <t>86,64; 89,68</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,29%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,09; 94,36</t>
+          <t>89,02; 94,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,43; 93,47</t>
+          <t>87,41; 93,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88,86; 94,24</t>
+          <t>88,96; 94,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82,05; 87,83</t>
+          <t>82,37; 87,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>88,97; 94,52</t>
+          <t>89,41; 94,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,52; 97,43</t>
+          <t>93,42; 97,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,2; 95,89</t>
+          <t>91,22; 96,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>84,88; 89,31</t>
+          <t>84,99; 89,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>90,06; 94,11</t>
+          <t>90,28; 93,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91,49; 94,96</t>
+          <t>91,54; 95,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91,08; 94,84</t>
+          <t>91,02; 94,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>84,07; 87,73</t>
+          <t>84,32; 87,92</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>88,5; 94,78</t>
+          <t>88,25; 94,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>92,61; 97,82</t>
+          <t>92,69; 97,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93,8; 97,96</t>
+          <t>93,58; 97,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85,39; 90,93</t>
+          <t>85,27; 90,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>92,13; 96,86</t>
+          <t>92,36; 96,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>95,24; 98,86</t>
+          <t>95,08; 98,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>91,94; 96,75</t>
+          <t>92,25; 96,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>89,52; 97,31</t>
+          <t>87,7; 91,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>91,69; 95,5</t>
+          <t>91,73; 95,44</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>94,98; 97,92</t>
+          <t>94,81; 97,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>93,72; 96,74</t>
+          <t>93,66; 96,76</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>88,86; 95,55</t>
+          <t>87,14; 90,79</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,26%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>91,27; 97,57</t>
+          <t>91,48; 97,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>90,09; 97,03</t>
+          <t>90,14; 97,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91,07; 96,37</t>
+          <t>91,0; 96,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86,61; 92,51</t>
+          <t>86,4; 92,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,55; 98,63</t>
+          <t>94,32; 98,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,24; 97,66</t>
+          <t>93,45; 97,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,98; 99,39</t>
+          <t>95,74; 99,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>88,77; 92,85</t>
+          <t>88,5; 92,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>94,34; 97,71</t>
+          <t>94,27; 97,62</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93,38; 96,93</t>
+          <t>93,45; 96,92</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>95,12; 97,76</t>
+          <t>94,96; 97,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,66; 92,08</t>
+          <t>88,33; 91,79</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,09%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>91,92; 93,75</t>
+          <t>91,94; 93,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>92,29; 94,22</t>
+          <t>92,41; 94,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>90,77; 92,78</t>
+          <t>90,76; 92,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86,42; 90,65</t>
+          <t>85,85; 88,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>93,47; 95,01</t>
+          <t>93,53; 95,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>93,27; 94,98</t>
+          <t>93,29; 94,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>93,22; 94,87</t>
+          <t>93,23; 94,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>82,61; 90,53</t>
+          <t>87,98; 89,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>92,91; 94,19</t>
+          <t>93,01; 94,18</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>93,13; 94,38</t>
+          <t>93,17; 94,35</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>92,33; 93,49</t>
+          <t>92,29; 93,51</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>85,02; 89,71</t>
+          <t>87,37; 88,83</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>351463</t>
+          <t>350929</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>286003</t>
+          <t>328872</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>637467</t>
+          <t>679802</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>451674; 474604</t>
+          <t>453121; 474453</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>419314; 437471</t>
+          <t>418380; 436912</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>385606; 404117</t>
+          <t>384056; 403775</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>327119; 369264</t>
+          <t>325260; 372911</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>425205; 445830</t>
+          <t>425023; 445124</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>385646; 407281</t>
+          <t>385265; 406951</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>350678; 371616</t>
+          <t>351147; 371932</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>271034; 296802</t>
+          <t>310258; 341705</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>884097; 913258</t>
+          <t>886342; 914486</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>809624; 839560</t>
+          <t>811472; 839611</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>742588; 770797</t>
+          <t>743258; 770669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>608701; 661637</t>
+          <t>649252; 702473</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365470</t>
+          <t>414650</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>392106</t>
+          <t>446725</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>757576</t>
+          <t>861374</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>678547; 704228</t>
+          <t>677346; 703952</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>623502; 651432</t>
+          <t>621148; 649824</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>509725; 540591</t>
+          <t>509994; 541709</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>345256; 380741</t>
+          <t>395312; 433535</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>577352; 600773</t>
+          <t>576749; 601160</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>544867; 572890</t>
+          <t>544187; 573054</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>517074; 538370</t>
+          <t>516365; 538441</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>232147; 459335</t>
+          <t>430423; 459765</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1262770; 1298799</t>
+          <t>1265624; 1299376</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1177694; 1216049</t>
+          <t>1178275; 1215870</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1036949; 1073849</t>
+          <t>1036802; 1073518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>571495; 826077</t>
+          <t>834741; 883261</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>469390</t>
+          <t>544470</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>476115</t>
+          <t>544130</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>945505</t>
+          <t>1088600</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>570667; 599329</t>
+          <t>569051; 597490</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>622785; 650720</t>
+          <t>621745; 650776</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>586982; 618834</t>
+          <t>586461; 617952</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>450421; 485013</t>
+          <t>524385; 561121</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>636918; 660799</t>
+          <t>636588; 662676</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>650708; 676889</t>
+          <t>651091; 677977</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>609195; 632732</t>
+          <t>609224; 631645</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>462657; 487483</t>
+          <t>527657; 557081</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1213965; 1252031</t>
+          <t>1214843; 1253532</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1282211; 1320585</t>
+          <t>1283816; 1321440</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1207028; 1246496</t>
+          <t>1203761; 1243894</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>922777; 965940</t>
+          <t>1065711; 1110818</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>804954</t>
+          <t>611976</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>638797</t>
+          <t>655814</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1443752</t>
+          <t>1267790</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>459216; 487242</t>
+          <t>458352; 487724</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>552505; 580772</t>
+          <t>551153; 579950</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>561569; 593409</t>
+          <t>560591; 592768</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>764179; 849743</t>
+          <t>591881; 629163</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>473931; 494721</t>
+          <t>474404; 495514</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>562373; 588337</t>
+          <t>561894; 588917</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>586516; 612592</t>
+          <t>585087; 613573</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>624152; 652444</t>
+          <t>642832; 668935</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>943332; 976778</t>
+          <t>942049; 977895</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1123355; 1162076</t>
+          <t>1124210; 1163440</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1155993; 1198228</t>
+          <t>1157480; 1197246</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1405474; 1499583</t>
+          <t>1245149; 1288868</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>476684</t>
+          <t>520101</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>478366</t>
+          <t>531027</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>955050</t>
+          <t>1051128</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>344518; 364916</t>
+          <t>344242; 365149</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>375462; 401389</t>
+          <t>375368; 401387</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>424699; 450368</t>
+          <t>425163; 450431</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>460494; 492952</t>
+          <t>501948; 535882</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>359418; 381845</t>
+          <t>361209; 382754</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>417825; 435284</t>
+          <t>417363; 435778</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>453136; 476440</t>
+          <t>453224; 477062</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>465055; 489341</t>
+          <t>517481; 542589</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>712117; 744123</t>
+          <t>713874; 742863</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>801611; 832051</t>
+          <t>802052; 833162</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>887862; 924484</t>
+          <t>887197; 922227</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>932493; 973037</t>
+          <t>1027224; 1071014</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>325944</t>
+          <t>359323</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>569497</t>
+          <t>394889</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>895441</t>
+          <t>754212</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>258921; 277308</t>
+          <t>258211; 276814</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>286882; 303021</t>
+          <t>287142; 302842</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>313598; 327501</t>
+          <t>312853; 326564</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>314375; 334778</t>
+          <t>347132; 369111</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>315936; 332161</t>
+          <t>316728; 332546</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>336200; 348981</t>
+          <t>335645; 348266</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>347331; 365500</t>
+          <t>348481; 365486</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>544631; 591987</t>
+          <t>385140; 402790</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>582696; 606942</t>
+          <t>582985; 606565</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>629500; 648988</t>
+          <t>628420; 648788</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>667349; 688879</t>
+          <t>666963; 689020</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>867759; 933070</t>
+          <t>737412; 768331</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>253567</t>
+          <t>278086</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>387801</t>
+          <t>421225</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>641368</t>
+          <t>699311</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>191557; 204791</t>
+          <t>191992; 204647</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>225094; 242438</t>
+          <t>225217; 242420</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>233243; 246818</t>
+          <t>233069; 247288</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>244884; 261578</t>
+          <t>268001; 285832</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>315720; 329329</t>
+          <t>314933; 328370</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>362669; 379867</t>
+          <t>363490; 380102</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>384067; 397708</t>
+          <t>383132; 396686</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>377991; 395385</t>
+          <t>411156; 431323</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>513038; 531328</t>
+          <t>512621; 530868</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>596537; 619247</t>
+          <t>596985; 619163</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>624241; 641567</t>
+          <t>623217; 641942</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>628264; 652455</t>
+          <t>684377; 711211</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3047473</t>
+          <t>3079536</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>3228685</t>
+          <t>3322683</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6276158</t>
+          <t>6402219</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3010865; 3070960</t>
+          <t>3011724; 3071974</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3161665; 3227948</t>
+          <t>3165996; 3224637</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3074831; 3142986</t>
+          <t>3074343; 3139692</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2989897; 3136156</t>
+          <t>3032838; 3124665</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3157344; 3209454</t>
+          <t>3159450; 3214503</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3313344; 3374125</t>
+          <t>3314081; 3372541</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3301378; 3359736</t>
+          <t>3301831; 3356938</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3024967; 3314975</t>
+          <t>3286012; 3355599</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6182195; 6267216</t>
+          <t>6188622; 6266671</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6498776; 6586109</t>
+          <t>6501487; 6583665</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6397489; 6478012</t>
+          <t>6394732; 6479156</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6055024; 6388820</t>
+          <t>6349366; 6455660</t>
         </is>
       </c>
     </row>
